--- a/upload/crib_2019.xlsx
+++ b/upload/crib_2019.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7210" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7290" uniqueCount="117">
   <si>
     <t>excluir</t>
   </si>
@@ -368,6 +368,9 @@
   <si>
     <t>06/2026</t>
   </si>
+  <si>
+    <t>07/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -692,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1441"/>
+  <dimension ref="A1:J1457"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -46807,6 +46810,518 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1442" spans="1:10">
+      <c r="A1442" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1442" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1442" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1442" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1442" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1442">
+        <v>0.09</v>
+      </c>
+      <c r="J1442" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:10">
+      <c r="A1443" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1443" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1443" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1443" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1443" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1443">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J1443" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:10">
+      <c r="A1444" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1444" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1444" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1444" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1444">
+        <v>0.73</v>
+      </c>
+      <c r="J1444" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:10">
+      <c r="A1445" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1445" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1445" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1445" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1445">
+        <v>0</v>
+      </c>
+      <c r="J1445" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:10">
+      <c r="A1446" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1446" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1446" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1446" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1446">
+        <v>0</v>
+      </c>
+      <c r="J1446" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:10">
+      <c r="A1447" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1447" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1447" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1447" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1447">
+        <v>0</v>
+      </c>
+      <c r="J1447" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:10">
+      <c r="A1448" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1448" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1448" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1448" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1448">
+        <v>0</v>
+      </c>
+      <c r="J1448" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:10">
+      <c r="A1449" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1449" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1449" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1449" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1449" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1449">
+        <v>0</v>
+      </c>
+      <c r="J1449" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:10">
+      <c r="A1450" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1450" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1450" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1450" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1450" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1450">
+        <v>0.1</v>
+      </c>
+      <c r="J1450" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:10">
+      <c r="A1451" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1451" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1451" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1451" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1451" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1451">
+        <v>0.6</v>
+      </c>
+      <c r="J1451" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:10">
+      <c r="A1452" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1452" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1452" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1452" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1452" s="2">
+        <v>1</v>
+      </c>
+      <c r="I1452">
+        <v>0.7</v>
+      </c>
+      <c r="J1452" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:10">
+      <c r="A1453" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1453" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1453" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1453" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1453" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1453">
+        <v>0</v>
+      </c>
+      <c r="J1453" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:10">
+      <c r="A1454" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1454" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1454" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1454" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1454" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1454">
+        <v>0</v>
+      </c>
+      <c r="J1454" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:10">
+      <c r="A1455" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1455" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1455" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1455" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1455" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1455">
+        <v>0</v>
+      </c>
+      <c r="J1455" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:10">
+      <c r="A1456" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1456" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1456" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1456" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1456" s="2">
+        <v>2</v>
+      </c>
+      <c r="I1456">
+        <v>1.5</v>
+      </c>
+      <c r="J1456" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:10">
+      <c r="A1457" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1457" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D1457" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1457" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1457" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1457">
+        <v>0</v>
+      </c>
+      <c r="J1457" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
